--- a/Python_Office_Automation/02-进阶提升让Excel飞起来/source_material/03/2019年某公司员工薪资表.xlsx
+++ b/Python_Office_Automation/02-进阶提升让Excel飞起来/source_material/03/2019年某公司员工薪资表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\python\Python_Office_Automation\02-进阶提升让Excel飞起来\source_material\03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD2B0D6-0E21-43A8-B952-FB4917E01929}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA86A852-5BD3-4D61-B861-3DB7FDF35265}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2430" yWindow="2790" windowWidth="28770" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2430" yWindow="2790" windowWidth="28770" windowHeight="15450" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -329,7 +329,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
@@ -343,33 +343,34 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -657,27 +658,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="7"/>
-      <c r="B1" s="8"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="7"/>
+      <c r="A1" s="5"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="5"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="13" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -689,20 +690,20 @@
       <c r="G2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="9" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
       <c r="E3" s="1" t="s">
         <v>6</v>
       </c>
@@ -712,15 +713,15 @@
       <c r="G3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -741,15 +742,15 @@
       <c r="G4" s="1">
         <v>3000</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="10">
         <v>3</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="9" t="s">
         <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -770,15 +771,15 @@
       <c r="G5" s="1">
         <v>2800</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="10">
         <v>2</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="9" t="s">
         <v>21</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -799,254 +800,254 @@
       <c r="G6" s="4">
         <v>2600</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="11">
         <v>3</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="9">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="9">
         <v>27</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="9">
         <v>2000</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="9">
         <v>2</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="9">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="9">
         <v>32</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="9">
         <v>2000</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="9">
         <v>3</v>
       </c>
-      <c r="I8" s="11"/>
+      <c r="I8" s="9"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="9">
         <v>36</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="9">
         <v>1500</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="9">
         <v>15</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="9">
         <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="9">
         <v>245</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="9">
         <v>1500</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="9">
         <v>4</v>
       </c>
-      <c r="I10" s="11"/>
+      <c r="I10" s="9"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="9">
         <v>29</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="9">
         <v>1500</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="9">
         <v>5</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="9">
         <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="9">
         <v>21</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="9">
         <v>1200</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="9">
         <v>6</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="9">
         <v>26</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="9">
         <v>1200</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="9">
         <v>4</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="9">
         <v>22</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="9">
         <v>1200</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="9">
         <v>3</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="9">
         <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5">
         <f>SUM(H4:H14)</f>
         <v>50</v>
       </c>
-      <c r="I15" s="7"/>
+      <c r="I15" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1062,9 +1063,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="14"/>
+      <c r="B1" s="14"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B2"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
